--- a/py_2/out.xlsx
+++ b/py_2/out.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C130"/>
+  <dimension ref="A1:C137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,12 +434,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>['40.114.177.156', '10.80.4.49', 443, 37765, 6]</t>
+          <t>['10.0.3.3', '10.0.3.4', 16830, 80, 6]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 37765</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 10.0.3.4 &amp;&amp; tcp.port == 16830 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -449,12 +449,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 54307, 17]</t>
+          <t>['10.0.3.3', '10.0.3.4', 49919, 80, 6]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 54307</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 10.0.3.4 &amp;&amp; tcp.port == 49919 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -464,12 +464,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 34144, 6]</t>
+          <t>['10.0.3.3', '100.29.244.21', 43149, 443, 6]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 34144</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 100.29.244.21 &amp;&amp; tcp.port == 43149 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -479,12 +479,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>['40.114.177.156', '10.80.4.49', 443, 50381, 6]</t>
+          <t>['10.0.3.3', '100.29.244.21', 55610, 443, 6]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 50381</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 100.29.244.21 &amp;&amp; tcp.port == 55610 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>['48.222.183.128', '10.80.4.49', 443, 29356, 6]</t>
+          <t>['10.0.3.3', '104.16.137.209', 57390, 443, 6]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ip.addr == 48.222.183.128 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 29356</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 104.16.137.209 &amp;&amp; tcp.port == 57390 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -509,12 +509,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>['10.80.4.49', '52.97.232.210', 1491, 443, 6]</t>
+          <t>['10.0.3.3', '104.16.138.209', 61849, 443, 6]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 52.97.232.210 &amp;&amp; tcp.port == 1491 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 104.16.138.209 &amp;&amp; tcp.port == 61849 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -524,12 +524,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 20872, 6]</t>
+          <t>['10.0.3.3', '104.16.140.209', 36361, 443, 6]</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 20872</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 104.16.140.209 &amp;&amp; tcp.port == 36361 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -539,12 +539,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>['172.217.208.93', '10.80.4.49', 443, 52869, 6]</t>
+          <t>['10.0.3.3', '104.17.91.187', 38727, 443, 6]</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ip.addr == 172.217.208.93 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 52869</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 104.17.91.187 &amp;&amp; tcp.port == 38727 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -554,12 +554,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 22251, 6]</t>
+          <t>['10.0.3.3', '104.17.92.187', 61891, 443, 6]</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 22251</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 104.17.92.187 &amp;&amp; tcp.port == 61891 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -569,12 +569,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>['40.114.177.156', '10.80.4.49', 443, 22877, 6]</t>
+          <t>['10.0.3.3', '104.18.17.5', 62444, 443, 6]</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 22877</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 104.18.17.5 &amp;&amp; tcp.port == 62444 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -584,12 +584,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>['143.204.55.73', '10.80.4.49', 443, 20609, 6]</t>
+          <t>['10.0.3.3', '104.18.38.142', 61766, 443, 6]</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ip.addr == 143.204.55.73 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 20609</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 104.18.38.142 &amp;&amp; tcp.port == 61766 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -599,12 +599,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>['143.204.55.79', '10.80.4.49', 443, 2036, 6]</t>
+          <t>['10.0.3.3', '104.18.40.68', 31815, 443, 6]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ip.addr == 143.204.55.79 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 2036</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 104.18.40.68 &amp;&amp; tcp.port == 31815 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -614,12 +614,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 60499, 17]</t>
+          <t>['10.0.3.3', '104.26.14.26', 35575, 443, 6]</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 60499</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 104.26.14.26 &amp;&amp; tcp.port == 35575 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -629,12 +629,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 10148, 6]</t>
+          <t>['10.0.3.3', '104.77.25.13', 15968, 443, 6]</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 10148</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 104.77.25.13 &amp;&amp; tcp.port == 15968 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -644,12 +644,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>['140.82.121.3', '10.80.4.49', 443, 9864, 6]</t>
+          <t>['10.0.3.3', '104.77.25.13', 33788, 443, 6]</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ip.addr == 140.82.121.3 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 9864</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 104.77.25.13 &amp;&amp; tcp.port == 33788 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -659,12 +659,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>['172.64.155.119', '10.80.4.49', 443, 58299, 6]</t>
+          <t>['10.0.3.3', '104.77.43.208', 6144, 443, 6]</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ip.addr == 172.64.155.119 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 58299</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 104.77.43.208 &amp;&amp; tcp.port == 6144 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -674,12 +674,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>['143.204.55.57', '10.80.4.49', 443, 13077, 6]</t>
+          <t>['10.0.3.3', '104.77.43.208', 46508, 443, 6]</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ip.addr == 143.204.55.57 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 13077</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 104.77.43.208 &amp;&amp; tcp.port == 46508 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -689,12 +689,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>['192.178.170.119', '10.80.4.49', 443, 55174, 6]</t>
+          <t>['10.0.3.3', '109.176.239.0', 31717, 443, 6]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ip.addr == 192.178.170.119 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 55174</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 109.176.239.0 &amp;&amp; tcp.port == 31717 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>['170.72.245.245', '10.80.4.49', 443, 49672, 6]</t>
+          <t>['10.0.3.3', '109.176.239.0', 41450, 443, 6]</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ip.addr == 170.72.245.245 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 49672</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 109.176.239.0 &amp;&amp; tcp.port == 41450 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -719,12 +719,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 49882, 6]</t>
+          <t>['10.0.3.3', '130.211.23.194', 28417, 443, 6]</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 49882</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 130.211.23.194 &amp;&amp; tcp.port == 28417 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>['142.251.127.84', '10.80.4.49', 443, 56861, 6]</t>
+          <t>['10.0.3.3', '143.204.50.133', 35071, 443, 6]</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ip.addr == 142.251.127.84 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 56861</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 143.204.50.133 &amp;&amp; tcp.port == 35071 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 57729, 17]</t>
+          <t>['10.0.3.3', '143.204.50.133', 51624, 443, 6]</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 57729</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 143.204.50.133 &amp;&amp; tcp.port == 51624 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -764,12 +764,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 53827, 6]</t>
+          <t>['10.0.3.3', '143.204.55.35', 43192, 443, 6]</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 53827</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 143.204.55.35 &amp;&amp; tcp.port == 43192 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>['188.114.97.12', '10.80.4.49', 443, 20583, 6]</t>
+          <t>['10.0.3.3', '143.204.55.80', 18371, 443, 6]</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ip.addr == 188.114.97.12 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 20583</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 143.204.55.80 &amp;&amp; tcp.port == 18371 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -794,12 +794,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>['147.93.42.49', '10.80.4.49', 443, 30452, 6]</t>
+          <t>['10.0.3.3', '143.204.55.82', 27556, 443, 6]</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ip.addr == 147.93.42.49 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 30452</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 143.204.55.82 &amp;&amp; tcp.port == 27556 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>['140.82.113.26', '10.80.4.49', 443, 20697, 6]</t>
+          <t>['10.0.3.3', '151.101.65.229', 37169, 443, 6]</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ip.addr == 140.82.113.26 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 20697</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 151.101.65.229 &amp;&amp; tcp.port == 37169 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -824,12 +824,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 25533, 6]</t>
+          <t>['10.0.3.3', '172.66.133.124', 46869, 443, 6]</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 25533</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 172.66.133.124 &amp;&amp; tcp.port == 46869 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -839,12 +839,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 14561, 6]</t>
+          <t>['10.0.3.3', '172.66.140.73', 13492, 443, 6]</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 14561</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 172.66.140.73 &amp;&amp; tcp.port == 13492 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 22703, 6]</t>
+          <t>['10.0.3.3', '172.66.148.140', 61340, 443, 6]</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 22703</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 172.66.148.140 &amp;&amp; tcp.port == 61340 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>['216.239.38.223', '10.80.4.49', 443, 25529, 6]</t>
+          <t>['10.0.3.3', '172.66.171.133', 7308, 443, 6]</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ip.addr == 216.239.38.223 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 25529</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 172.66.171.133 &amp;&amp; tcp.port == 7308 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -884,12 +884,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>['40.114.177.156', '10.80.4.49', 443, 41908, 6]</t>
+          <t>['10.0.3.3', '172.66.171.133', 31122, 443, 6]</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 41908</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 172.66.171.133 &amp;&amp; tcp.port == 31122 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 64137, 17]</t>
+          <t>['10.0.3.3', '172.66.171.133', 61644, 443, 6]</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 64137</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 172.66.171.133 &amp;&amp; tcp.port == 61644 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 52664, 17]</t>
+          <t>['10.0.3.3', '172.67.142.245', 56530, 443, 6]</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 52664</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 172.67.142.245 &amp;&amp; tcp.port == 56530 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 49885, 6]</t>
+          <t>['10.0.3.3', '172.67.184.158', 48650, 443, 6]</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 49885</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 172.67.184.158 &amp;&amp; tcp.port == 48650 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>['151.101.67.42', '10.80.4.49', 443, 26767, 6]</t>
+          <t>['10.0.3.3', '185.199.108.153', 36308, 443, 6]</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ip.addr == 151.101.67.42 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 26767</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 185.199.108.153 &amp;&amp; tcp.port == 36308 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>['151.101.67.42', '10.80.4.49', 443, 45261, 6]</t>
+          <t>['10.0.3.3', '199.232.142.132', 49134, 443, 6]</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ip.addr == 151.101.67.42 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 45261</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 199.232.142.132 &amp;&amp; tcp.port == 49134 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 55681, 17]</t>
+          <t>['10.0.3.3', '20.250.198.32', 8505, 443, 6]</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 55681</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 20.250.198.32 &amp;&amp; tcp.port == 8505 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>['40.114.177.156', '10.80.4.49', 443, 41895, 6]</t>
+          <t>['10.0.3.3', '34.200.97.200', 41485, 443, 6]</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 41895</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 34.200.97.200 &amp;&amp; tcp.port == 41485 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>['40.114.177.156', '10.80.4.49', 443, 41909, 6]</t>
+          <t>['10.0.3.3', '34.36.200.111', 47817, 443, 6]</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 41909</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 34.36.200.111 &amp;&amp; tcp.port == 47817 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 22932, 6]</t>
+          <t>['10.0.3.3', '34.98.107.242', 4764, 443, 6]</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 22932</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 34.98.107.242 &amp;&amp; tcp.port == 4764 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 20670, 6]</t>
+          <t>['10.0.3.3', '34.98.107.242', 38925, 443, 6]</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 20670</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 34.98.107.242 &amp;&amp; tcp.port == 38925 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>['147.93.42.49', '10.80.4.49', 443, 54167, 6]</t>
+          <t>['10.0.3.3', '35.83.71.196', 16026, 443, 6]</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ip.addr == 147.93.42.49 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 54167</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 35.83.71.196 &amp;&amp; tcp.port == 16026 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>['40.114.177.156', '10.80.4.49', 443, 41913, 6]</t>
+          <t>['10.0.3.3', '35.83.71.196', 56704, 443, 6]</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 41913</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 35.83.71.196 &amp;&amp; tcp.port == 56704 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>['40.114.177.156', '10.80.4.49', 443, 50379, 6]</t>
+          <t>['10.0.3.3', '40.114.177.156', 14936, 443, 6]</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 50379</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 40.114.177.156 &amp;&amp; tcp.port == 14936 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 26729, 6]</t>
+          <t>['10.0.3.3', '40.114.177.156', 16405, 443, 6]</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 26729</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 40.114.177.156 &amp;&amp; tcp.port == 16405 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>['143.204.51.60', '10.80.4.49', 443, 16076, 6]</t>
+          <t>['10.0.3.3', '40.114.177.156', 19451, 443, 6]</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ip.addr == 143.204.51.60 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 16076</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 40.114.177.156 &amp;&amp; tcp.port == 19451 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>['208.109.33.25', '10.80.4.49', 443, 65184, 6]</t>
+          <t>['10.0.3.3', '40.114.177.156', 49615, 443, 6]</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ip.addr == 208.109.33.25 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 65184</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 40.114.177.156 &amp;&amp; tcp.port == 49615 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>['3.165.190.104', '10.80.4.49', 443, 6705, 6]</t>
+          <t>['10.0.3.3', '40.114.177.156', 49860, 443, 6]</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ip.addr == 3.165.190.104 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 6705</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 40.114.177.156 &amp;&amp; tcp.port == 49860 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 25457, 6]</t>
+          <t>['10.0.3.3', '40.114.177.156', 52453, 443, 6]</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 25457</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 40.114.177.156 &amp;&amp; tcp.port == 52453 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 53588, 17]</t>
+          <t>['10.0.3.3', '40.114.177.156', 57314, 443, 6]</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 53588</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 40.114.177.156 &amp;&amp; tcp.port == 57314 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 6212, 6]</t>
+          <t>['10.0.3.3', '40.114.177.156', 58069, 443, 6]</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 6212</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 40.114.177.156 &amp;&amp; tcp.port == 58069 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>['40.114.177.156', '10.80.4.49', 443, 50376, 6]</t>
+          <t>['10.0.3.3', '40.114.177.156', 58226, 443, 6]</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 50376</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 40.114.177.156 &amp;&amp; tcp.port == 58226 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 63315, 6]</t>
+          <t>['10.0.3.3', '40.114.177.156', 64698, 443, 6]</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 63315</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 40.114.177.156 &amp;&amp; tcp.port == 64698 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 55100, 6]</t>
+          <t>['10.0.3.3', '40.114.177.156', 65245, 443, 6]</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 55100</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 40.114.177.156 &amp;&amp; tcp.port == 65245 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 29617, 6]</t>
+          <t>['10.0.3.3', '40.114.178.124', 1560, 443, 6]</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 29617</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 40.114.178.124 &amp;&amp; tcp.port == 1560 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>['88.214.205.144', '10.80.4.49', 443, 58240, 6]</t>
+          <t>['10.0.3.3', '40.114.178.124', 4524, 443, 6]</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ip.addr == 88.214.205.144 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 58240</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 40.114.178.124 &amp;&amp; tcp.port == 4524 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 14260, 6]</t>
+          <t>['10.0.3.3', '40.114.178.124', 16069, 443, 6]</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 14260</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 40.114.178.124 &amp;&amp; tcp.port == 16069 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 34393, 6]</t>
+          <t>['10.0.3.3', '40.114.178.124', 35490, 443, 6]</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 34393</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 40.114.178.124 &amp;&amp; tcp.port == 35490 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>['40.114.177.156', '10.80.4.49', 443, 3234, 6]</t>
+          <t>['10.0.3.3', '40.114.178.124', 61868, 443, 6]</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 3234</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 40.114.178.124 &amp;&amp; tcp.port == 61868 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 5498, 6]</t>
+          <t>['10.0.3.3', '52.159.82.83', 2102, 443, 6]</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 5498</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 52.159.82.83 &amp;&amp; tcp.port == 2102 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>['104.77.25.13', '10.80.4.49', 443, 6830, 6]</t>
+          <t>['10.0.3.3', '52.159.82.83', 23679, 443, 6]</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ip.addr == 104.77.25.13 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 6830</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 52.159.82.83 &amp;&amp; tcp.port == 23679 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 25265, 6]</t>
+          <t>['10.0.3.3', '52.159.82.83', 62037, 443, 6]</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 25265</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 52.159.82.83 &amp;&amp; tcp.port == 62037 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 19383, 6]</t>
+          <t>['10.0.3.3', '69.163.176.189', 17257, 443, 6]</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 19383</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 69.163.176.189 &amp;&amp; tcp.port == 17257 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 1908, 6]</t>
+          <t>['10.0.3.3', '69.163.176.189', 36628, 443, 6]</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 1908</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 69.163.176.189 &amp;&amp; tcp.port == 36628 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 14636, 6]</t>
+          <t>['10.0.3.3', '91.99.163.163', 9064, 443, 6]</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 14636</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 91.99.163.163 &amp;&amp; tcp.port == 9064 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 21603, 6]</t>
+          <t>['10.0.3.3', '91.99.163.163', 48532, 443, 6]</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 21603</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 91.99.163.163 &amp;&amp; tcp.port == 48532 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>['140.82.113.25', '10.80.4.49', 443, 33907, 6]</t>
+          <t>['10.0.3.3', '91.99.163.163', 55759, 443, 6]</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ip.addr == 140.82.113.25 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 33907</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 91.99.163.163 &amp;&amp; tcp.port == 55759 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 54124, 17]</t>
+          <t>['10.0.3.3', '99.80.3.199', 21895, 443, 6]</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 54124</t>
+          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 99.80.3.199 &amp;&amp; tcp.port == 21895 &amp;&amp; tcp.port == 443</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 34044, 6]</t>
+          <t>['10.0.3.4', '10.0.3.3', 80, 35345, 6]</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 34044</t>
+          <t>ip.addr == 10.0.3.4 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 35345</t>
         </is>
       </c>
     </row>
@@ -1469,12 +1469,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 60527, 6]</t>
+          <t>['100.29.244.21', '10.0.3.3', 443, 65526, 6]</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 60527</t>
+          <t>ip.addr == 100.29.244.21 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 65526</t>
         </is>
       </c>
     </row>
@@ -1484,12 +1484,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>['16.63.106.243', '10.80.4.49', 443, 46336, 6]</t>
+          <t>['104.16.75.142', '10.0.3.3', 443, 58790, 6]</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ip.addr == 16.63.106.243 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 46336</t>
+          <t>ip.addr == 104.16.75.142 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 58790</t>
         </is>
       </c>
     </row>
@@ -1499,12 +1499,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 51798, 6]</t>
+          <t>['104.16.76.142', '10.0.3.3', 443, 7266, 6]</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 51798</t>
+          <t>ip.addr == 104.16.76.142 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 7266</t>
         </is>
       </c>
     </row>
@@ -1514,12 +1514,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 9730, 6]</t>
+          <t>['104.16.79.142', '10.0.3.3', 443, 38224, 6]</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 9730</t>
+          <t>ip.addr == 104.16.79.142 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 38224</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 52044, 6]</t>
+          <t>['104.17.26.24', '10.0.3.3', 443, 34085, 6]</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 52044</t>
+          <t>ip.addr == 104.17.26.24 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 34085</t>
         </is>
       </c>
     </row>
@@ -1544,12 +1544,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 32643, 6]</t>
+          <t>['104.18.16.5', '10.0.3.3', 443, 58342, 6]</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 32643</t>
+          <t>ip.addr == 104.18.16.5 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 58342</t>
         </is>
       </c>
     </row>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>['40.114.177.156', '10.80.4.49', 443, 52045, 6]</t>
+          <t>['104.18.17.5', '10.0.3.3', 443, 62854, 6]</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 52045</t>
+          <t>ip.addr == 104.18.17.5 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 62854</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>['52.178.17.2', '10.80.4.49', 443, 41567, 6]</t>
+          <t>['104.18.38.142', '10.0.3.3', 443, 16788, 6]</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ip.addr == 52.178.17.2 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 41567</t>
+          <t>ip.addr == 104.18.38.142 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 16788</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>['52.178.17.2', '10.80.4.49', 443, 38865, 6]</t>
+          <t>['104.18.40.68', '10.0.3.3', 443, 32334, 6]</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ip.addr == 52.178.17.2 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 38865</t>
+          <t>ip.addr == 104.18.40.68 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 32334</t>
         </is>
       </c>
     </row>
@@ -1604,12 +1604,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 58752, 6]</t>
+          <t>['104.18.40.68', '10.0.3.3', 443, 35486, 6]</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 58752</t>
+          <t>ip.addr == 104.18.40.68 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 35486</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 26278, 6]</t>
+          <t>['104.18.40.68', '10.0.3.3', 443, 42649, 6]</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 26278</t>
+          <t>ip.addr == 104.18.40.68 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 42649</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>['40.114.177.156', '10.80.4.49', 443, 41905, 6]</t>
+          <t>['104.18.40.68', '10.0.3.3', 443, 62667, 6]</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 41905</t>
+          <t>ip.addr == 104.18.40.68 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 62667</t>
         </is>
       </c>
     </row>
@@ -1649,12 +1649,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>['40.114.177.156', '10.80.4.49', 443, 10339, 6]</t>
+          <t>['104.20.20.189', '10.0.3.3', 443, 49195, 6]</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 10339</t>
+          <t>ip.addr == 104.20.20.189 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 49195</t>
         </is>
       </c>
     </row>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 17466, 6]</t>
+          <t>['104.77.25.13', '10.0.3.3', 443, 1317, 6]</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 17466</t>
+          <t>ip.addr == 104.77.25.13 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 1317</t>
         </is>
       </c>
     </row>
@@ -1679,12 +1679,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>['40.114.177.156', '10.80.4.49', 443, 50375, 6]</t>
+          <t>['104.77.25.13', '10.0.3.3', 443, 40875, 6]</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 50375</t>
+          <t>ip.addr == 104.77.25.13 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 40875</t>
         </is>
       </c>
     </row>
@@ -1694,12 +1694,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>['13.107.13.93', '10.80.4.49', 443, 54863, 6]</t>
+          <t>['104.77.25.13', '10.0.3.3', 443, 57595, 6]</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ip.addr == 13.107.13.93 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 54863</t>
+          <t>ip.addr == 104.77.25.13 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 57595</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 36390, 6]</t>
+          <t>['104.77.43.208', '10.0.3.3', 443, 65492, 6]</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 36390</t>
+          <t>ip.addr == 104.77.43.208 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 65492</t>
         </is>
       </c>
     </row>
@@ -1724,12 +1724,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>['23.11.41.157', '10.80.4.49', 80, 61585, 6]</t>
+          <t>['109.176.239.0', '10.0.3.3', 443, 62843, 6]</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ip.addr == 23.11.41.157 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 61585</t>
+          <t>ip.addr == 109.176.239.0 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 62843</t>
         </is>
       </c>
     </row>
@@ -1739,12 +1739,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 65309, 6]</t>
+          <t>['116.202.167.127', '10.0.3.3', 443, 43526, 6]</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 65309</t>
+          <t>ip.addr == 116.202.167.127 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 43526</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 10329, 6]</t>
+          <t>['141.193.213.21', '10.0.3.3', 443, 8495, 6]</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 10329</t>
+          <t>ip.addr == 141.193.213.21 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 8495</t>
         </is>
       </c>
     </row>
@@ -1769,12 +1769,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>['192.178.170.94', '10.80.4.49', 443, 35565, 6]</t>
+          <t>['143.204.55.80', '10.0.3.3', 443, 22955, 6]</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ip.addr == 192.178.170.94 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 35565</t>
+          <t>ip.addr == 143.204.55.80 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 22955</t>
         </is>
       </c>
     </row>
@@ -1784,12 +1784,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>['40.114.177.156', '10.80.4.49', 443, 19414, 6]</t>
+          <t>['143.204.55.96', '10.0.3.3', 443, 36031, 6]</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 19414</t>
+          <t>ip.addr == 143.204.55.96 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 36031</t>
         </is>
       </c>
     </row>
@@ -1799,12 +1799,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>['172.187.86.72', '10.80.4.49', 443, 49539, 6]</t>
+          <t>['151.101.129.229', '10.0.3.3', 443, 8563, 6]</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ip.addr == 172.187.86.72 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 49539</t>
+          <t>ip.addr == 151.101.129.229 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 8563</t>
         </is>
       </c>
     </row>
@@ -1814,12 +1814,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 17140, 6]</t>
+          <t>['151.101.193.229', '10.0.3.3', 443, 4259, 6]</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 17140</t>
+          <t>ip.addr == 151.101.193.229 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 4259</t>
         </is>
       </c>
     </row>
@@ -1829,12 +1829,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 16461, 6]</t>
+          <t>['162.159.152.4', '10.0.3.3', 443, 18831, 6]</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 16461</t>
+          <t>ip.addr == 162.159.152.4 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 18831</t>
         </is>
       </c>
     </row>
@@ -1844,12 +1844,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 1803, 6]</t>
+          <t>['162.159.153.4', '10.0.3.3', 443, 49912, 6]</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 1803</t>
+          <t>ip.addr == 162.159.153.4 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 49912</t>
         </is>
       </c>
     </row>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 53337, 6]</t>
+          <t>['172.64.146.132', '10.0.3.3', 443, 34917, 6]</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 53337</t>
+          <t>ip.addr == 172.64.146.132 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 34917</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 9139, 6]</t>
+          <t>['172.66.147.243', '10.0.3.3', 443, 19450, 6]</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 9139</t>
+          <t>ip.addr == 172.66.147.243 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 19450</t>
         </is>
       </c>
     </row>
@@ -1889,12 +1889,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>['40.114.177.156', '10.80.4.49', 443, 6361, 6]</t>
+          <t>['172.66.148.140', '10.0.3.3', 443, 6213, 6]</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 6361</t>
+          <t>ip.addr == 172.66.148.140 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 6213</t>
         </is>
       </c>
     </row>
@@ -1904,12 +1904,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 5936, 6]</t>
+          <t>['172.66.171.133', '10.0.3.3', 443, 23869, 6]</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 5936</t>
+          <t>ip.addr == 172.66.171.133 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 23869</t>
         </is>
       </c>
     </row>
@@ -1919,12 +1919,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 59850, 17]</t>
+          <t>['172.66.171.133', '10.0.3.3', 443, 52852, 6]</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 59850</t>
+          <t>ip.addr == 172.66.171.133 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 52852</t>
         </is>
       </c>
     </row>
@@ -1934,12 +1934,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 64799, 6]</t>
+          <t>['172.67.189.47', '10.0.3.3', 443, 10844, 6]</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 64799</t>
+          <t>ip.addr == 172.67.189.47 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 10844</t>
         </is>
       </c>
     </row>
@@ -1949,12 +1949,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>['170.72.245.187', '10.80.4.49', 443, 54861, 6]</t>
+          <t>['18.97.36.56', '10.0.3.3', 443, 26023, 6]</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ip.addr == 170.72.245.187 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 54861</t>
+          <t>ip.addr == 18.97.36.56 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 26023</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 65321, 6]</t>
+          <t>['192.0.76.3', '10.0.3.3', 443, 47439, 6]</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 65321</t>
+          <t>ip.addr == 192.0.76.3 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 47439</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>['40.114.177.156', '10.80.4.49', 443, 14647, 6]</t>
+          <t>['192.178.170.141', '10.0.3.3', 443, 40875, 6]</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 14647</t>
+          <t>ip.addr == 192.178.170.141 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 40875</t>
         </is>
       </c>
     </row>
@@ -1994,12 +1994,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 52047, 6]</t>
+          <t>['193.246.48.184', '10.0.3.3', 443, 53782, 6]</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 52047</t>
+          <t>ip.addr == 193.246.48.184 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 53782</t>
         </is>
       </c>
     </row>
@@ -2009,12 +2009,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>['100.26.86.112', '10.80.4.49', 443, 36879, 6]</t>
+          <t>['193.247.41.19', '10.0.3.3', 443, 23271, 6]</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ip.addr == 100.26.86.112 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 36879</t>
+          <t>ip.addr == 193.247.41.19 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 23271</t>
         </is>
       </c>
     </row>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>['143.204.55.106', '10.80.4.49', 443, 52887, 6]</t>
+          <t>['193.247.41.19', '10.0.3.3', 443, 27281, 6]</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>ip.addr == 143.204.55.106 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 52887</t>
+          <t>ip.addr == 193.247.41.19 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 27281</t>
         </is>
       </c>
     </row>
@@ -2039,12 +2039,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 2680, 6]</t>
+          <t>['2.21.22.144', '10.0.3.3', 443, 12827, 6]</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 2680</t>
+          <t>ip.addr == 2.21.22.144 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 12827</t>
         </is>
       </c>
     </row>
@@ -2054,12 +2054,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 49664, 17]</t>
+          <t>['34.160.81.0', '10.0.3.3', 443, 22081, 6]</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 49664</t>
+          <t>ip.addr == 34.160.81.0 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 22081</t>
         </is>
       </c>
     </row>
@@ -2069,12 +2069,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 57623, 6]</t>
+          <t>['34.98.107.242', '10.0.3.3', 443, 33057, 6]</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 57623</t>
+          <t>ip.addr == 34.98.107.242 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 33057</t>
         </is>
       </c>
     </row>
@@ -2084,12 +2084,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>['104.18.9.17', '10.80.4.49', 443, 64703, 6]</t>
+          <t>['40.114.177.156', '10.0.3.3', 443, 17522, 6]</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ip.addr == 104.18.9.17 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 64703</t>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 17522</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>['146.190.62.39', '10.80.4.49', 80, 21609, 6]</t>
+          <t>['40.114.177.156', '10.0.3.3', 443, 21853, 6]</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 21609</t>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 21853</t>
         </is>
       </c>
     </row>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 11187, 6]</t>
+          <t>['40.114.177.156', '10.0.3.3', 443, 27674, 6]</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 11187</t>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 27674</t>
         </is>
       </c>
     </row>
@@ -2129,12 +2129,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 5179, 6]</t>
+          <t>['40.114.177.156', '10.0.3.3', 443, 27765, 6]</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 5179</t>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 27765</t>
         </is>
       </c>
     </row>
@@ -2144,12 +2144,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 3114, 6]</t>
+          <t>['40.114.177.156', '10.0.3.3', 443, 33546, 6]</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 3114</t>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 33546</t>
         </is>
       </c>
     </row>
@@ -2159,12 +2159,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 8280, 6]</t>
+          <t>['40.114.177.156', '10.0.3.3', 443, 42894, 6]</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 8280</t>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 42894</t>
         </is>
       </c>
     </row>
@@ -2174,12 +2174,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>['204.62.13.147', '10.80.4.49', 443, 63482, 6]</t>
+          <t>['40.114.177.156', '10.0.3.3', 443, 47478, 6]</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ip.addr == 204.62.13.147 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 63482</t>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 47478</t>
         </is>
       </c>
     </row>
@@ -2189,12 +2189,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 49384, 6]</t>
+          <t>['40.114.177.156', '10.0.3.3', 443, 56983, 6]</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 49384</t>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 56983</t>
         </is>
       </c>
     </row>
@@ -2204,12 +2204,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>['40.114.177.156', '10.80.4.49', 443, 10335, 6]</t>
+          <t>['40.114.177.156', '10.0.3.3', 443, 59065, 6]</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 10335</t>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 59065</t>
         </is>
       </c>
     </row>
@@ -2219,12 +2219,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 41894, 6]</t>
+          <t>['40.114.177.156', '10.0.3.3', 443, 60395, 6]</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 41894</t>
+          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 60395</t>
         </is>
       </c>
     </row>
@@ -2234,12 +2234,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 51947, 17]</t>
+          <t>['40.114.178.124', '10.0.3.3', 443, 52722, 6]</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 51947</t>
+          <t>ip.addr == 40.114.178.124 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 52722</t>
         </is>
       </c>
     </row>
@@ -2249,12 +2249,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 61935, 6]</t>
+          <t>['48.222.183.128', '10.0.3.3', 443, 41024, 6]</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 61935</t>
+          <t>ip.addr == 48.222.183.128 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 41024</t>
         </is>
       </c>
     </row>
@@ -2264,12 +2264,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>['204.62.13.147', '10.80.4.49', 443, 50560, 6]</t>
+          <t>['52.159.82.83', '10.0.3.3', 443, 5559, 6]</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ip.addr == 204.62.13.147 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 50560</t>
+          <t>ip.addr == 52.159.82.83 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 5559</t>
         </is>
       </c>
     </row>
@@ -2279,12 +2279,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>['37.252.171.21', '10.80.4.49', 443, 58765, 6]</t>
+          <t>['52.159.82.83', '10.0.3.3', 443, 11106, 6]</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ip.addr == 37.252.171.21 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 58765</t>
+          <t>ip.addr == 52.159.82.83 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 11106</t>
         </is>
       </c>
     </row>
@@ -2294,12 +2294,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 62572, 6]</t>
+          <t>['52.159.82.83', '10.0.3.3', 443, 46417, 6]</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 62572</t>
+          <t>ip.addr == 52.159.82.83 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 46417</t>
         </is>
       </c>
     </row>
@@ -2309,12 +2309,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>['10.80.1.4', '10.80.4.49', 53, 59775, 17]</t>
+          <t>['52.159.82.83', '10.0.3.3', 443, 47460, 6]</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.1.4 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 53 &amp;&amp; tcp.port == 59775</t>
+          <t>ip.addr == 52.159.82.83 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 47460</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>['150.171.110.56', '10.80.4.49', 443, 6360, 6]</t>
+          <t>['52.159.82.83', '10.0.3.3', 443, 60922, 6]</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>ip.addr == 150.171.110.56 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 6360</t>
+          <t>ip.addr == 52.159.82.83 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 60922</t>
         </is>
       </c>
     </row>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>['10.80.4.49', '170.72.0.137', 35113, 443, 6]</t>
+          <t>['52.213.7.252', '10.0.3.3', 443, 59982, 6]</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 170.72.0.137 &amp;&amp; tcp.port == 35113 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 52.213.7.252 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 59982</t>
         </is>
       </c>
     </row>
@@ -2354,12 +2354,117 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>['52.112.122.38', '10.80.4.49', 443, 58677, 6]</t>
+          <t>['69.163.176.189', '10.0.3.3', 443, 18096, 6]</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>ip.addr == 52.112.122.38 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 58677</t>
+          <t>ip.addr == 69.163.176.189 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 18096</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>['69.163.176.189', '10.0.3.3', 443, 61024, 6]</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>ip.addr == 69.163.176.189 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 61024</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>['75.2.60.68', '10.0.3.3', 443, 25751, 6]</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>ip.addr == 75.2.60.68 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 25751</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>['80.74.141.2', '10.0.3.3', 443, 5982, 6]</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>ip.addr == 80.74.141.2 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 5982</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>['87.106.173.199', '10.0.3.3', 443, 14993, 6]</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>ip.addr == 87.106.173.199 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 14993</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>['89.187.165.194', '10.0.3.3', 443, 17655, 6]</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>ip.addr == 89.187.165.194 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 17655</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>['91.99.163.163', '10.0.3.3', 443, 6451, 6]</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>ip.addr == 91.99.163.163 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 6451</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>['91.99.163.163', '10.0.3.3', 443, 18018, 6]</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>ip.addr == 91.99.163.163 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 18018</t>
         </is>
       </c>
     </row>

--- a/py_2/out.xlsx
+++ b/py_2/out.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C137"/>
+  <dimension ref="A1:C131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,12 +434,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '10.0.3.4', 16830, 80, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 1149, 80, 6]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 10.0.3.4 &amp;&amp; tcp.port == 16830 &amp;&amp; tcp.port == 80</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 1149 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -449,12 +449,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '10.0.3.4', 49919, 80, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 1154, 80, 6]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 10.0.3.4 &amp;&amp; tcp.port == 49919 &amp;&amp; tcp.port == 80</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 1154 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -464,12 +464,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '100.29.244.21', 43149, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 3046, 80, 6]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 100.29.244.21 &amp;&amp; tcp.port == 43149 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 3046 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -479,12 +479,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '100.29.244.21', 55610, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 3052, 80, 6]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 100.29.244.21 &amp;&amp; tcp.port == 55610 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 3052 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '104.16.137.209', 57390, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 3220, 80, 6]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 104.16.137.209 &amp;&amp; tcp.port == 57390 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 3220 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -509,12 +509,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '104.16.138.209', 61849, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 6369, 80, 6]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 104.16.138.209 &amp;&amp; tcp.port == 61849 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 6369 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -524,12 +524,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '104.16.140.209', 36361, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 9137, 80, 6]</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 104.16.140.209 &amp;&amp; tcp.port == 36361 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 9137 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -539,12 +539,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '104.17.91.187', 38727, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 9139, 80, 6]</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 104.17.91.187 &amp;&amp; tcp.port == 38727 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 9139 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -554,12 +554,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '104.17.92.187', 61891, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 10322, 80, 6]</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 104.17.92.187 &amp;&amp; tcp.port == 61891 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 10322 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -569,12 +569,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '104.18.17.5', 62444, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 14260, 80, 6]</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 104.18.17.5 &amp;&amp; tcp.port == 62444 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 14260 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -584,12 +584,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '104.18.38.142', 61766, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 14633, 80, 6]</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 104.18.38.142 &amp;&amp; tcp.port == 61766 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 14633 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -599,12 +599,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '104.18.40.68', 31815, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 14636, 80, 6]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 104.18.40.68 &amp;&amp; tcp.port == 31815 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 14636 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -614,12 +614,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '104.26.14.26', 35575, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 14642, 80, 6]</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 104.26.14.26 &amp;&amp; tcp.port == 35575 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 14642 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -629,12 +629,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '104.77.25.13', 15968, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 17140, 80, 6]</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 104.77.25.13 &amp;&amp; tcp.port == 15968 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 17140 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -644,12 +644,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '104.77.25.13', 33788, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 19977, 80, 6]</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 104.77.25.13 &amp;&amp; tcp.port == 33788 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 19977 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -659,12 +659,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '104.77.43.208', 6144, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 19979, 80, 6]</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 104.77.43.208 &amp;&amp; tcp.port == 6144 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 19979 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -674,12 +674,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '104.77.43.208', 46508, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 20232, 80, 6]</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 104.77.43.208 &amp;&amp; tcp.port == 46508 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 20232 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -689,12 +689,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '109.176.239.0', 31717, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 20673, 80, 6]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 109.176.239.0 &amp;&amp; tcp.port == 31717 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 20673 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '109.176.239.0', 41450, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 20675, 80, 6]</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 109.176.239.0 &amp;&amp; tcp.port == 41450 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 20675 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -719,12 +719,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '130.211.23.194', 28417, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 20699, 80, 6]</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 130.211.23.194 &amp;&amp; tcp.port == 28417 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 20699 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '143.204.50.133', 35071, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 21052, 80, 6]</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 143.204.50.133 &amp;&amp; tcp.port == 35071 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 21052 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '143.204.50.133', 51624, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 21584, 80, 6]</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 143.204.50.133 &amp;&amp; tcp.port == 51624 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 21584 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -764,12 +764,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '143.204.55.35', 43192, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 21597, 80, 6]</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 143.204.55.35 &amp;&amp; tcp.port == 43192 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 21597 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '143.204.55.80', 18371, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 21600, 80, 6]</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 143.204.55.80 &amp;&amp; tcp.port == 18371 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 21600 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -794,12 +794,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '143.204.55.82', 27556, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 21603, 80, 6]</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 143.204.55.82 &amp;&amp; tcp.port == 27556 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 21603 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '151.101.65.229', 37169, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 21607, 80, 6]</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 151.101.65.229 &amp;&amp; tcp.port == 37169 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 21607 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -824,12 +824,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '172.66.133.124', 46869, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 21609, 80, 6]</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 172.66.133.124 &amp;&amp; tcp.port == 46869 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 21609 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -839,12 +839,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '172.66.140.73', 13492, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 24451, 80, 6]</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 172.66.140.73 &amp;&amp; tcp.port == 13492 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 24451 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '172.66.148.140', 61340, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 24754, 80, 6]</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 172.66.148.140 &amp;&amp; tcp.port == 61340 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 24754 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '172.66.171.133', 7308, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 25530, 80, 6]</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 172.66.171.133 &amp;&amp; tcp.port == 7308 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 25530 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -884,12 +884,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '172.66.171.133', 31122, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 25533, 80, 6]</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 172.66.171.133 &amp;&amp; tcp.port == 31122 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 25533 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '172.66.171.133', 61644, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 25537, 80, 6]</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 172.66.171.133 &amp;&amp; tcp.port == 61644 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 25537 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '172.67.142.245', 56530, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 26278, 80, 6]</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 172.67.142.245 &amp;&amp; tcp.port == 56530 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 26278 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '172.67.184.158', 48650, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 27220, 80, 6]</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 172.67.184.158 &amp;&amp; tcp.port == 48650 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 27220 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '185.199.108.153', 36308, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 27224, 80, 6]</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 185.199.108.153 &amp;&amp; tcp.port == 36308 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 27224 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '199.232.142.132', 49134, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 27226, 80, 6]</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 199.232.142.132 &amp;&amp; tcp.port == 49134 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 27226 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '20.250.198.32', 8505, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 36880, 80, 6]</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 20.250.198.32 &amp;&amp; tcp.port == 8505 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 36880 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '34.200.97.200', 41485, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 41895, 80, 6]</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 34.200.97.200 &amp;&amp; tcp.port == 41485 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 41895 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '34.36.200.111', 47817, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 41896, 80, 6]</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 34.36.200.111 &amp;&amp; tcp.port == 47817 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 41896 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '34.98.107.242', 4764, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 41899, 80, 6]</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 34.98.107.242 &amp;&amp; tcp.port == 4764 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 41899 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '34.98.107.242', 38925, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 41902, 80, 6]</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 34.98.107.242 &amp;&amp; tcp.port == 38925 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 41902 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '35.83.71.196', 16026, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 44339, 80, 6]</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 35.83.71.196 &amp;&amp; tcp.port == 16026 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 44339 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '35.83.71.196', 56704, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 44342, 80, 6]</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 35.83.71.196 &amp;&amp; tcp.port == 56704 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 44342 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '40.114.177.156', 14936, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 44345, 80, 6]</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 40.114.177.156 &amp;&amp; tcp.port == 14936 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 44345 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '40.114.177.156', 16405, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 45008, 80, 6]</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 40.114.177.156 &amp;&amp; tcp.port == 16405 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 45008 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '40.114.177.156', 19451, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 46269, 80, 6]</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 40.114.177.156 &amp;&amp; tcp.port == 19451 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 46269 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '40.114.177.156', 49615, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 49878, 80, 6]</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 40.114.177.156 &amp;&amp; tcp.port == 49615 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 49878 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '40.114.177.156', 49860, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 49882, 80, 6]</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 40.114.177.156 &amp;&amp; tcp.port == 49860 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 49882 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '40.114.177.156', 52453, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 50366, 80, 6]</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 40.114.177.156 &amp;&amp; tcp.port == 52453 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 50366 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '40.114.177.156', 57314, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 51131, 80, 6]</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 40.114.177.156 &amp;&amp; tcp.port == 57314 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 51131 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '40.114.177.156', 58069, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 51134, 80, 6]</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 40.114.177.156 &amp;&amp; tcp.port == 58069 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 51134 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '40.114.177.156', 58226, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 52016, 80, 6]</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 40.114.177.156 &amp;&amp; tcp.port == 58226 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 52016 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '40.114.177.156', 64698, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 52044, 80, 6]</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 40.114.177.156 &amp;&amp; tcp.port == 64698 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 52044 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '40.114.177.156', 65245, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 52047, 80, 6]</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 40.114.177.156 &amp;&amp; tcp.port == 65245 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 52047 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '40.114.178.124', 1560, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 52050, 80, 6]</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 40.114.178.124 &amp;&amp; tcp.port == 1560 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 52050 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '40.114.178.124', 4524, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 52052, 80, 6]</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 40.114.178.124 &amp;&amp; tcp.port == 4524 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 52052 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '40.114.178.124', 16069, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 52055, 80, 6]</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 40.114.178.124 &amp;&amp; tcp.port == 16069 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 52055 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '40.114.178.124', 35490, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 54083, 80, 6]</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 40.114.178.124 &amp;&amp; tcp.port == 35490 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 54083 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '40.114.178.124', 61868, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 54857, 80, 6]</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 40.114.178.124 &amp;&amp; tcp.port == 61868 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 54857 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '52.159.82.83', 2102, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 54868, 80, 6]</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 52.159.82.83 &amp;&amp; tcp.port == 2102 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 54868 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '52.159.82.83', 23679, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 54870, 80, 6]</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 52.159.82.83 &amp;&amp; tcp.port == 23679 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 54870 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '52.159.82.83', 62037, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 54883, 80, 6]</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 52.159.82.83 &amp;&amp; tcp.port == 62037 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 54883 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '69.163.176.189', 17257, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 54886, 80, 6]</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 69.163.176.189 &amp;&amp; tcp.port == 17257 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 54886 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '69.163.176.189', 36628, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 54894, 80, 6]</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 69.163.176.189 &amp;&amp; tcp.port == 36628 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 54894 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '91.99.163.163', 9064, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 54899, 80, 6]</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 91.99.163.163 &amp;&amp; tcp.port == 9064 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 54899 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '91.99.163.163', 48532, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 60528, 80, 6]</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 91.99.163.163 &amp;&amp; tcp.port == 48532 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 60528 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '91.99.163.163', 55759, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 60530, 80, 6]</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 91.99.163.163 &amp;&amp; tcp.port == 55759 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 60530 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>['10.0.3.3', '99.80.3.199', 21895, 443, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 60533, 80, 6]</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.3 &amp;&amp; ip.addr == 99.80.3.199 &amp;&amp; tcp.port == 21895 &amp;&amp; tcp.port == 443</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 60533 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>['10.0.3.4', '10.0.3.3', 80, 35345, 6]</t>
+          <t>['10.80.4.49', '146.190.62.39', 64799, 80, 6]</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ip.addr == 10.0.3.4 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 35345</t>
+          <t>ip.addr == 10.80.4.49 &amp;&amp; ip.addr == 146.190.62.39 &amp;&amp; tcp.port == 64799 &amp;&amp; tcp.port == 80</t>
         </is>
       </c>
     </row>
@@ -1469,12 +1469,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>['100.29.244.21', '10.0.3.3', 443, 65526, 6]</t>
+          <t>['140.82.112.26', '10.80.4.49', 443, 2116, 6]</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ip.addr == 100.29.244.21 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 65526</t>
+          <t>ip.addr == 140.82.112.26 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 2116</t>
         </is>
       </c>
     </row>
@@ -1484,12 +1484,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>['104.16.75.142', '10.0.3.3', 443, 58790, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 1152, 6]</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ip.addr == 104.16.75.142 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 58790</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 1152</t>
         </is>
       </c>
     </row>
@@ -1499,12 +1499,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>['104.16.76.142', '10.0.3.3', 443, 7266, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 1190, 6]</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ip.addr == 104.16.76.142 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 7266</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 1190</t>
         </is>
       </c>
     </row>
@@ -1514,12 +1514,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>['104.16.79.142', '10.0.3.3', 443, 38224, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 3048, 6]</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ip.addr == 104.16.79.142 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 38224</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 3048</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>['104.17.26.24', '10.0.3.3', 443, 34085, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 3233, 6]</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ip.addr == 104.17.26.24 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 34085</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 3233</t>
         </is>
       </c>
     </row>
@@ -1544,12 +1544,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>['104.18.16.5', '10.0.3.3', 443, 58342, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 6364, 6]</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ip.addr == 104.18.16.5 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 58342</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 6364</t>
         </is>
       </c>
     </row>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>['104.18.17.5', '10.0.3.3', 443, 62854, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 6366, 6]</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ip.addr == 104.18.17.5 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 62854</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 6366</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>['104.18.38.142', '10.0.3.3', 443, 16788, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 10318, 6]</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ip.addr == 104.18.38.142 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 16788</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 10318</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>['104.18.40.68', '10.0.3.3', 443, 32334, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 10329, 6]</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ip.addr == 104.18.40.68 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 32334</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 10329</t>
         </is>
       </c>
     </row>
@@ -1604,12 +1604,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>['104.18.40.68', '10.0.3.3', 443, 35486, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 11828, 6]</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ip.addr == 104.18.40.68 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 35486</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 11828</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>['104.18.40.68', '10.0.3.3', 443, 42649, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 14089, 6]</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ip.addr == 104.18.40.68 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 42649</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 14089</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>['104.18.40.68', '10.0.3.3', 443, 62667, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 14630, 6]</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ip.addr == 104.18.40.68 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 62667</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 14630</t>
         </is>
       </c>
     </row>
@@ -1649,12 +1649,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>['104.20.20.189', '10.0.3.3', 443, 49195, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 14639, 6]</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ip.addr == 104.20.20.189 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 49195</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 14639</t>
         </is>
       </c>
     </row>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>['104.77.25.13', '10.0.3.3', 443, 1317, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 14644, 6]</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ip.addr == 104.77.25.13 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 1317</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 14644</t>
         </is>
       </c>
     </row>
@@ -1679,12 +1679,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>['104.77.25.13', '10.0.3.3', 443, 40875, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 14649, 6]</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ip.addr == 104.77.25.13 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 40875</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 14649</t>
         </is>
       </c>
     </row>
@@ -1694,12 +1694,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>['104.77.25.13', '10.0.3.3', 443, 57595, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 14651, 6]</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ip.addr == 104.77.25.13 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 57595</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 14651</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>['104.77.43.208', '10.0.3.3', 443, 65492, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 17535, 6]</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ip.addr == 104.77.43.208 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 65492</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 17535</t>
         </is>
       </c>
     </row>
@@ -1724,12 +1724,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>['109.176.239.0', '10.0.3.3', 443, 62843, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 19982, 6]</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ip.addr == 109.176.239.0 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 62843</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 19982</t>
         </is>
       </c>
     </row>
@@ -1739,12 +1739,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>['116.202.167.127', '10.0.3.3', 443, 43526, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 20236, 6]</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ip.addr == 116.202.167.127 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 43526</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 20236</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>['141.193.213.21', '10.0.3.3', 443, 8495, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 20239, 6]</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ip.addr == 141.193.213.21 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 8495</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 20239</t>
         </is>
       </c>
     </row>
@@ -1769,12 +1769,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>['143.204.55.80', '10.0.3.3', 443, 22955, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 20377, 6]</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ip.addr == 143.204.55.80 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 22955</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 20377</t>
         </is>
       </c>
     </row>
@@ -1784,12 +1784,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>['143.204.55.96', '10.0.3.3', 443, 36031, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 20667, 6]</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ip.addr == 143.204.55.96 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 36031</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 20667</t>
         </is>
       </c>
     </row>
@@ -1799,12 +1799,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>['151.101.129.229', '10.0.3.3', 443, 8563, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 20670, 6]</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ip.addr == 151.101.129.229 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 8563</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 20670</t>
         </is>
       </c>
     </row>
@@ -1814,12 +1814,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>['151.101.193.229', '10.0.3.3', 443, 4259, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 21312, 6]</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ip.addr == 151.101.193.229 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 4259</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 21312</t>
         </is>
       </c>
     </row>
@@ -1829,12 +1829,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>['162.159.152.4', '10.0.3.3', 443, 18831, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 21594, 6]</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ip.addr == 162.159.152.4 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 18831</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 21594</t>
         </is>
       </c>
     </row>
@@ -1844,12 +1844,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>['162.159.153.4', '10.0.3.3', 443, 49912, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 23428, 6]</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ip.addr == 162.159.153.4 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 49912</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 23428</t>
         </is>
       </c>
     </row>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>['172.64.146.132', '10.0.3.3', 443, 34917, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 24453, 6]</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ip.addr == 172.64.146.132 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 34917</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 24453</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>['172.66.147.243', '10.0.3.3', 443, 19450, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 24705, 6]</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ip.addr == 172.66.147.243 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 19450</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 24705</t>
         </is>
       </c>
     </row>
@@ -1889,12 +1889,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>['172.66.148.140', '10.0.3.3', 443, 6213, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 24751, 6]</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ip.addr == 172.66.148.140 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 6213</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 24751</t>
         </is>
       </c>
     </row>
@@ -1904,12 +1904,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>['172.66.171.133', '10.0.3.3', 443, 23869, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 24757, 6]</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ip.addr == 172.66.171.133 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 23869</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 24757</t>
         </is>
       </c>
     </row>
@@ -1919,12 +1919,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>['172.66.171.133', '10.0.3.3', 443, 52852, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 25540, 6]</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ip.addr == 172.66.171.133 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 52852</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 25540</t>
         </is>
       </c>
     </row>
@@ -1934,12 +1934,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>['172.67.189.47', '10.0.3.3', 443, 10844, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 26276, 6]</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ip.addr == 172.67.189.47 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 10844</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 26276</t>
         </is>
       </c>
     </row>
@@ -1949,12 +1949,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>['18.97.36.56', '10.0.3.3', 443, 26023, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 27205, 6]</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ip.addr == 18.97.36.56 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 26023</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 27205</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>['192.0.76.3', '10.0.3.3', 443, 47439, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 31307, 6]</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ip.addr == 192.0.76.3 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 47439</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 31307</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>['192.178.170.141', '10.0.3.3', 443, 40875, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 33910, 6]</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ip.addr == 192.178.170.141 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 40875</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 33910</t>
         </is>
       </c>
     </row>
@@ -1994,12 +1994,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>['193.246.48.184', '10.0.3.3', 443, 53782, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 36234, 6]</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>ip.addr == 193.246.48.184 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 53782</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 36234</t>
         </is>
       </c>
     </row>
@@ -2009,12 +2009,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>['193.247.41.19', '10.0.3.3', 443, 23271, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 36237, 6]</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ip.addr == 193.247.41.19 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 23271</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 36237</t>
         </is>
       </c>
     </row>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>['193.247.41.19', '10.0.3.3', 443, 27281, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 36557, 6]</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>ip.addr == 193.247.41.19 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 27281</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 36557</t>
         </is>
       </c>
     </row>
@@ -2039,12 +2039,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>['2.21.22.144', '10.0.3.3', 443, 12827, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 41892, 6]</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ip.addr == 2.21.22.144 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 12827</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 41892</t>
         </is>
       </c>
     </row>
@@ -2054,12 +2054,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>['34.160.81.0', '10.0.3.3', 443, 22081, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 41897, 6]</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ip.addr == 34.160.81.0 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 22081</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 41897</t>
         </is>
       </c>
     </row>
@@ -2069,12 +2069,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>['34.98.107.242', '10.0.3.3', 443, 33057, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 41898, 6]</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>ip.addr == 34.98.107.242 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 33057</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 41898</t>
         </is>
       </c>
     </row>
@@ -2084,12 +2084,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>['40.114.177.156', '10.0.3.3', 443, 17522, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 41903, 6]</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 17522</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 41903</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>['40.114.177.156', '10.0.3.3', 443, 21853, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 44336, 6]</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 21853</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 44336</t>
         </is>
       </c>
     </row>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>['40.114.177.156', '10.0.3.3', 443, 27674, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 48189, 6]</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 27674</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 48189</t>
         </is>
       </c>
     </row>
@@ -2129,12 +2129,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>['40.114.177.156', '10.0.3.3', 443, 27765, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 49874, 6]</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 27765</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 49874</t>
         </is>
       </c>
     </row>
@@ -2144,12 +2144,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>['40.114.177.156', '10.0.3.3', 443, 33546, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 49885, 6]</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 33546</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 49885</t>
         </is>
       </c>
     </row>
@@ -2159,12 +2159,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>['40.114.177.156', '10.0.3.3', 443, 42894, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 51136, 6]</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 42894</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 51136</t>
         </is>
       </c>
     </row>
@@ -2174,12 +2174,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>['40.114.177.156', '10.0.3.3', 443, 47478, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 51139, 6]</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 47478</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 51139</t>
         </is>
       </c>
     </row>
@@ -2189,12 +2189,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>['40.114.177.156', '10.0.3.3', 443, 56983, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 52041, 6]</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 56983</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 52041</t>
         </is>
       </c>
     </row>
@@ -2204,12 +2204,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>['40.114.177.156', '10.0.3.3', 443, 59065, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 52057, 6]</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 59065</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 52057</t>
         </is>
       </c>
     </row>
@@ -2219,12 +2219,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>['40.114.177.156', '10.0.3.3', 443, 60395, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 53797, 6]</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ip.addr == 40.114.177.156 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 60395</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 53797</t>
         </is>
       </c>
     </row>
@@ -2234,12 +2234,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>['40.114.178.124', '10.0.3.3', 443, 52722, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 54081, 6]</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>ip.addr == 40.114.178.124 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 52722</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 54081</t>
         </is>
       </c>
     </row>
@@ -2249,12 +2249,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>['48.222.183.128', '10.0.3.3', 443, 41024, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 54086, 6]</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ip.addr == 48.222.183.128 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 41024</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 54086</t>
         </is>
       </c>
     </row>
@@ -2264,12 +2264,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>['52.159.82.83', '10.0.3.3', 443, 5559, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 54874, 6]</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ip.addr == 52.159.82.83 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 5559</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 54874</t>
         </is>
       </c>
     </row>
@@ -2279,12 +2279,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>['52.159.82.83', '10.0.3.3', 443, 11106, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 54880, 6]</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ip.addr == 52.159.82.83 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 11106</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 54880</t>
         </is>
       </c>
     </row>
@@ -2294,12 +2294,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>['52.159.82.83', '10.0.3.3', 443, 46417, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 54888, 6]</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ip.addr == 52.159.82.83 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 46417</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 54888</t>
         </is>
       </c>
     </row>
@@ -2309,12 +2309,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>['52.159.82.83', '10.0.3.3', 443, 47460, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 54891, 6]</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ip.addr == 52.159.82.83 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 47460</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 54891</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>['52.159.82.83', '10.0.3.3', 443, 60922, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 54897, 6]</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>ip.addr == 52.159.82.83 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 60922</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 54897</t>
         </is>
       </c>
     </row>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>['52.213.7.252', '10.0.3.3', 443, 59982, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 61586, 6]</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ip.addr == 52.213.7.252 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 59982</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 61586</t>
         </is>
       </c>
     </row>
@@ -2354,12 +2354,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>['69.163.176.189', '10.0.3.3', 443, 18096, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 64716, 6]</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>ip.addr == 69.163.176.189 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 18096</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 64716</t>
         </is>
       </c>
     </row>
@@ -2369,102 +2369,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>['69.163.176.189', '10.0.3.3', 443, 61024, 6]</t>
+          <t>['146.190.62.39', '10.80.4.49', 80, 64721, 6]</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>ip.addr == 69.163.176.189 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 61024</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="n">
-        <v>130</v>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>['75.2.60.68', '10.0.3.3', 443, 25751, 6]</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>ip.addr == 75.2.60.68 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 25751</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="n">
-        <v>131</v>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>['80.74.141.2', '10.0.3.3', 443, 5982, 6]</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>ip.addr == 80.74.141.2 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 5982</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="n">
-        <v>132</v>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>['87.106.173.199', '10.0.3.3', 443, 14993, 6]</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>ip.addr == 87.106.173.199 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 14993</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="n">
-        <v>133</v>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>['89.187.165.194', '10.0.3.3', 443, 17655, 6]</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>ip.addr == 89.187.165.194 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 17655</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="n">
-        <v>134</v>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>['91.99.163.163', '10.0.3.3', 443, 6451, 6]</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>ip.addr == 91.99.163.163 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 6451</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="n">
-        <v>135</v>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>['91.99.163.163', '10.0.3.3', 443, 18018, 6]</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>ip.addr == 91.99.163.163 &amp;&amp; ip.addr == 10.0.3.3 &amp;&amp; tcp.port == 443 &amp;&amp; tcp.port == 18018</t>
+          <t>ip.addr == 146.190.62.39 &amp;&amp; ip.addr == 10.80.4.49 &amp;&amp; tcp.port == 80 &amp;&amp; tcp.port == 64721</t>
         </is>
       </c>
     </row>
